--- a/mom-trip-days-1-24.xlsx
+++ b/mom-trip-days-1-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2486" uniqueCount="962">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2486" uniqueCount="964">
   <si>
     <t>Mom's Canyon Trip 2026 — What You're Doing Each Day</t>
   </si>
@@ -52,7 +52,7 @@
     <t>Note ⚠️</t>
   </si>
   <si>
-    <t>Land at Salt Lake City Airport (SLC) at 9:35 AM. Plan ~1.5 hours for deplaning, baggage claim, and rental-car pickup before starting the drive.</t>
+    <t>Land at Salt Lake City airport (SLC) at 09:35. Plan about 1.5 hours to deplane, collect bags, and pick up the rental car before heading out.</t>
   </si>
   <si>
     <t>~1.5 hrs</t>
@@ -67,19 +67,25 @@
     <t>In the car</t>
   </si>
   <si>
-    <t>Pick up the rental car at Salt Lake City Airport. Then drive about 3.5 hours south to Moab, Utah. The highway passes through beautiful mountain and canyon country — enjoy the scenery on the way in.</t>
+    <t>Pick up the rental car at Salt Lake City airport and head out — about a 3.5 hour drive south to Moab, Utah. The road passes through beautiful mountains and canyons. Enjoy the scenery on the way.</t>
   </si>
   <si>
     <t>~3.5 hrs</t>
   </si>
   <si>
+    <t>40.79069</t>
+  </si>
+  <si>
+    <t>-111.97715</t>
+  </si>
+  <si>
     <t>~3:00 PM</t>
   </si>
   <si>
     <t>Sleep tonight 🏨</t>
   </si>
   <si>
-    <t>Sun Outdoor Arches Gateway — Moab, UT</t>
+    <t>Sun Outdoor Arches Gateway — Moab, Utah</t>
   </si>
   <si>
     <t>38.60099</t>
@@ -94,7 +100,7 @@
     <t>7:00 AM</t>
   </si>
   <si>
-    <t>Drive 15 minutes from the hotel to Arches National Park entrance.</t>
+    <t>A 15 minute drive from the hotel to the entrance of Arches National Park.</t>
   </si>
   <si>
     <t>15 min</t>
@@ -106,7 +112,7 @@
     <t>Quick stop</t>
   </si>
   <si>
-    <t>Stop at the Arches Visitor Center to pick up your park pass and map.</t>
+    <t>Stop at the Arches Visitor Center to pick up the park entry pass and a map.</t>
   </si>
   <si>
     <t>10 min</t>
@@ -124,7 +130,7 @@
     <t>Hike</t>
   </si>
   <si>
-    <t>Park Avenue Trail — walk between towering sandstone walls, like a natural hallway carved by nature. Flat and easy.</t>
+    <t>Park Avenue Trail — walk between tall sandstone walls, like a natural corridor carved by nature. Flat and easy.</t>
   </si>
   <si>
     <t>1.5 hrs</t>
@@ -139,7 +145,7 @@
     <t>9:10 AM</t>
   </si>
   <si>
-    <t>As you drive deeper into the park, the La Sal Mountains appear to your right — stay in the car and enjoy the view through the window.</t>
+    <t>Continue deeper into the park. The La Sal Mountains appear on the right — stay in the car and enjoy the view through the window.</t>
   </si>
   <si>
     <t>5 min</t>
@@ -148,7 +154,7 @@
     <t>9:15 AM</t>
   </si>
   <si>
-    <t>Courthouse Towers — pull over, look at the tall red rock towers rising from the desert, take a photo.</t>
+    <t>Courthouse Towers — pull over by the road, look at the huge red rock towers rising from the desert, and take photos.</t>
   </si>
   <si>
     <t>38.63255</t>
@@ -163,7 +169,7 @@
     <t>Short walk</t>
   </si>
   <si>
-    <t>Balanced Rock — a short easy loop around a famous giant rock perfectly balanced on a thin base.</t>
+    <t>Balanced Rock — a short, easy loop around a famous huge rock balanced perfectly on a thin base.</t>
   </si>
   <si>
     <t>20 min</t>
@@ -178,13 +184,13 @@
     <t>10:00 AM</t>
   </si>
   <si>
-    <t>Windows section — from one parking area you walk to three different arches: Turret Arch, the Windows Loop, and Double Arch. You can stand under some of them — they are enormous.</t>
+    <t>The Windows section — from one parking lot you can walk to three different arches: Turret Arch, the Windows Loop, and Double Arch. You can stand under several of them — they are huge.</t>
   </si>
   <si>
     <t>11:45 AM</t>
   </si>
   <si>
-    <t>Delicate Arch Trail — the most famous arch in the world. A steep walk on open slickrock in the sun. Bring extra water. Worth every step.</t>
+    <t>Delicate Arch Trail — the world-famous arch. A steep walk on open slickrock in the sun. Bring extra water. Worth every step.</t>
   </si>
   <si>
     <t>2.5–3 hrs</t>
@@ -199,7 +205,7 @@
     <t>2:40 PM</t>
   </si>
   <si>
-    <t>Fiery Furnace Viewpoint — pull over and look into the narrow maze of rock fins from a fence. You cannot enter without a guided tour.</t>
+    <t>Fiery Furnace Viewpoint — pull over and look from the railing into the narrow maze of rock fins. Entry without a guided tour or permit is not allowed.</t>
   </si>
   <si>
     <t>38.74262</t>
@@ -211,7 +217,7 @@
     <t>2:52 PM</t>
   </si>
   <si>
-    <t>Skyline Arch — visible from the road. Pull over for a quick photo.</t>
+    <t>Skyline Arch — visible from the road. Stop for a quick photo.</t>
   </si>
   <si>
     <t>38.77500</t>
@@ -223,7 +229,7 @@
     <t>3:00 PM</t>
   </si>
   <si>
-    <t>Sand Dune Arch + Broken Arch — two arches on a short side trail near the road. Sand Dune is a 0.4mi walk through deep sand to a small arch sheltered between rock fins (cool and shaded — kids love the sand). Broken Arch is another 0.4mi across slickrock to a large arch. They are usually combined in one stop.</t>
+    <t>Sand Dune Arch + Broken Arch — two arches on a short side trail by the road. Sand Dune is about 0.6 km through deep sand to a small arch hidden between rock fins (cool and shaded — kids love the sand). Broken Arch is another 0.6 km on open slickrock to a large arch. Most people combine the two into one stop.</t>
   </si>
   <si>
     <t>45 min</t>
@@ -241,7 +247,7 @@
     <t>3:50 PM</t>
   </si>
   <si>
-    <t>Devils Garden — the best trail in all of Arches. On the way in you pass Tunnel Arch and Pine Tree Arch, then reach Landscape Arch (the longest natural arch in the world). From there the primitive trail continues deeper to Partition Arch, Navajo Arch, Double O Arch, Dark Angel, and Private Arch — each arch a different shape, and the trail grows quieter and more remote the further you go.</t>
+    <t>Devils Garden — the best trail in all of Arches. On the way in you pass Tunnel Arch and Pine Tree Arch, then reach Landscape Arch (the longest natural arch in the world). From there the primitive trail continues deeper to Partition Arch, Navajo Arch, Double O Arch, Dark Angel, and Private Arch — each arch a different shape, and the trail gets quieter and more remote the further you go.</t>
   </si>
   <si>
     <t>2–4 hrs</t>
@@ -259,7 +265,7 @@
     <t>~7:00 PM</t>
   </si>
   <si>
-    <t>Sun Outdoors Arches Gateway — Moab, UT (same hotel)</t>
+    <t>Sun Outdoors Arches Gateway — Moab, Utah (same hotel)</t>
   </si>
   <si>
     <t>38.60109</t>
@@ -274,7 +280,7 @@
     <t>Day 3  —  Thu, May 7, 2026     Canyonlands + Fiery Furnace     Wake up 6:30 AM  |  Leave at 7:20 AM</t>
   </si>
   <si>
-    <t>Drive 35 minutes from the hotel into Arches National Park to the Fiery Furnace parking lot. You already have your park pass from yesterday — no need to stop at the Visitor Center. Take a screenshot of the Recreation.gov ticket before driving in (cell service is poor at the trailhead).</t>
+    <t>A 35 minute drive from the hotel into Arches National Park to the Fiery Furnace parking lot. You already have the park entry pass from yesterday — no need to stop at the Visitor Center. Take a screenshot of the Recreation.gov permit before driving in (cell signal is weak at the trailhead).</t>
   </si>
   <si>
     <t>35 min</t>
@@ -286,7 +292,7 @@
     <t>8:00 AM</t>
   </si>
   <si>
-    <t>Self-Guided Fiery Furnace Exploration — confirmed permit Rec.gov #0816993222-1, 8:00 AM start, 2 adults. Route-find through a maze of sandstone fins on slickrock. No marked trail — narrow squeezes between walls, small jumps between rocks, ledges. Roughly 2 miles round trip but takes much longer than the distance suggests because you navigate visually. Plan a full 3.5 hours. Bring water, snacks, and grippy shoes. NOT a casual walk — this is the strenuous one mom asked for.</t>
+    <t>Self-Guided Fiery Furnace Exploration — permit approved for 2 adults, start at 08:00. You navigate the maze of sandstone fins on open slickrock on your own. There is no marked trail — narrow passages between walls, small jumps between rocks, rock steps. About 3 km round-trip, but it takes far longer than the distance suggests because you find your own way. Plan a full 3.5 hours. Bring water, snacks, and shoes with good grip. This is not an easy walk — it is the challenging hike Mom asked for.</t>
   </si>
   <si>
     <t>3.5 hrs</t>
@@ -304,7 +310,7 @@
     <t>11:30 AM</t>
   </si>
   <si>
-    <t>Drive ~55 minutes from Fiery Furnace to Dead Horse Point — exit Arches south on the park road, north a short stretch on Highway 191, then west on Highway 313 across the mesa.</t>
+    <t>About a 55 minute drive from Fiery Furnace to Dead Horse Point — exit Arches south on the park road, a short stretch north on Highway 191, then west on Highway 313 across the mesa.</t>
   </si>
   <si>
     <t>55 min</t>
@@ -316,7 +322,7 @@
     <t>12:25 PM</t>
   </si>
   <si>
-    <t>Dead Horse Point — walk to the canyon rim. The Colorado River flows 2,000 feet below in a horseshoe bend. One of the most breathtaking views in Utah. Quick lunch from the cooler on a bench at the rim.</t>
+    <t>Dead Horse Point — walk to the canyon rim. The Colorado River flows 600 meters below in a horseshoe bend. One of the most striking viewpoints in Utah. A short lunch from the cooler on a bench at the canyon edge.</t>
   </si>
   <si>
     <t>60 min</t>
@@ -334,7 +340,7 @@
     <t>1:25 PM</t>
   </si>
   <si>
-    <t>Drive 15 minutes from Dead Horse Point to the Canyonlands Island in the Sky entrance.</t>
+    <t>A 15 minute drive from Dead Horse Point to the entrance of Canyonlands Island in the Sky.</t>
   </si>
   <si>
     <t>⏰ TIME — was 10:00 AM</t>
@@ -343,7 +349,7 @@
     <t>1:40 PM</t>
   </si>
   <si>
-    <t>Shafer Canyon Overlook — pull over and look down at the road that spirals into the canyon far below.</t>
+    <t>Shafer Canyon Overlook — pull over and look down at the road that switchbacks far into the canyon below.</t>
   </si>
   <si>
     <t>38.45300</t>
@@ -358,7 +364,7 @@
     <t>1:52 PM</t>
   </si>
   <si>
-    <t>Gooseneck Overlook — the Colorado River bends 270 degrees into a tight loop below you. Very dramatic.</t>
+    <t>Gooseneck Overlook — the Colorado River bends 270 degrees into a tight loop below. Very dramatic.</t>
   </si>
   <si>
     <t>38.45575</t>
@@ -373,7 +379,7 @@
     <t>2:02 PM</t>
   </si>
   <si>
-    <t>Drive 20 minutes across the mesa to Upheaval Dome on the far side of the park.</t>
+    <t>A 20 minute drive across the mesa to Upheaval Dome at the far side of the park.</t>
   </si>
   <si>
     <t>⏰ TIME — was 10:37 AM</t>
@@ -382,7 +388,7 @@
     <t>2:22 PM</t>
   </si>
   <si>
-    <t>Upheaval Dome — a short walk to the edge of a mysterious crater. Scientists are not sure if a meteor made it or a salt dome — either way, it looks like something from another planet.</t>
+    <t>Upheaval Dome — a short walk to the rim of a mysterious crater. Scientists are not sure whether a meteorite made it or a salt dome — either way, it looks like something from another planet.</t>
   </si>
   <si>
     <t>38.42919</t>
@@ -397,7 +403,7 @@
     <t>3:07 PM</t>
   </si>
   <si>
-    <t>Whale Rock — a big whale-shaped sandstone dome right next to Upheaval Dome. Short 1-mile trail with some easy scrambling up the slickrock. From the top you get the best view of Upheaval Dome from above.</t>
+    <t>Whale Rock — a large whale-shaped sandstone dome right next to Upheaval Dome. A short 1.6 km trail with an easy climb on open slickrock. From the top you see Upheaval Dome from above — the best view of it.</t>
   </si>
   <si>
     <t>⏰ TIME — was 11:45 AM</t>
@@ -415,7 +421,7 @@
     <t>4:12 PM</t>
   </si>
   <si>
-    <t>Mesa Arch — a half-mile easy walk to a sandstone arch framing the canyon 1,000 feet below.</t>
+    <t>Mesa Arch — an easy 0.8 km walk to a sandstone arch that frames the canyon 300 meters below.</t>
   </si>
   <si>
     <t>25 min</t>
@@ -433,7 +439,7 @@
     <t>4:37 PM</t>
   </si>
   <si>
-    <t>Green River Overlook, Murphy Point, and Buck Canyon Overlook — pull over at each of these three spots for canyon views. Each is a short walk from the car.</t>
+    <t>Green River Overlook, Murphy Point and Buck Canyon Overlook — stop at each of the three viewpoints for canyon views. Each one is a short walk from the car.</t>
   </si>
   <si>
     <t>10–15 min each</t>
@@ -451,7 +457,7 @@
     <t>5:07 PM</t>
   </si>
   <si>
-    <t>White Rim Overlook — short 0.9-mile easy walk out to a point with a clear view straight down onto the White Rim Road winding through the canyon below. Good spot to sit and see how far the canyon drops.</t>
+    <t>White Rim Overlook — an easy 1.5 km walk to a viewpoint that looks straight down at White Rim Road winding through the canyon. A good place to sit and see how deep the canyon really is.</t>
   </si>
   <si>
     <t>30 min</t>
@@ -466,13 +472,13 @@
     <t>⏰ TIME — was 1:50 PM</t>
   </si>
   <si>
-    <t>Musselman Arch — a famous long flat arch you may have read about. It sits on the White Rim Road about 1,000 feet below you. Driving to it requires a 4WD vehicle and a permit — NOT doable in your rental car. You can see the top of it from some of the rim overlooks on a clear day.</t>
+    <t>Musselman Arch — a long flat famous arch you may have read about. It sits on White Rim Road about 300 meters below you. Reaching it requires a 4-by-4 vehicle and a permit — not possible in your rental car. On a clear day you can see the top of it from some of the overlooks.</t>
   </si>
   <si>
     <t>5:37 PM</t>
   </si>
   <si>
-    <t>Grand View Point — the end of the main road. Walk along the canyon rim in all directions. The best panoramic views in Canyonlands.</t>
+    <t>Grand View Point — the end of the main park road. Walk along the canyon rim in any direction. The best panoramic views in Canyonlands.</t>
   </si>
   <si>
     <t>38.30785</t>
@@ -487,7 +493,7 @@
     <t>6:22 PM</t>
   </si>
   <si>
-    <t>Drive ~30 minutes south on Hwy 313/191 back into Moab.</t>
+    <t>About a 30 minute drive south on Highways 313 and 191 back to Moab.</t>
   </si>
   <si>
     <t>🗑️ REPLACED — old Hwy 128/Fisher Towers segment removed (Fisher Towers dropped to fit Fiery Furnace morning)</t>
@@ -496,7 +502,7 @@
     <t>~6:55 PM</t>
   </si>
   <si>
-    <t>The Bowen Motel — Moab, UT</t>
+    <t>The Bowen Motel — Moab, Utah</t>
   </si>
   <si>
     <t>38.57599</t>
@@ -610,6 +616,12 @@
     <t>Bentonite Hills — rainbow-striped clay badlands. No official trails — walk where others have walked. A famously Mars-like landscape.</t>
   </si>
   <si>
+    <t>38.41960</t>
+  </si>
+  <si>
+    <t>-110.91010</t>
+  </si>
+  <si>
     <t>12:20 PM</t>
   </si>
   <si>
@@ -967,12 +979,6 @@
     <t>Dukes Slickrock Campground &amp; RV — Hanksville, UT (same camp, second night)</t>
   </si>
   <si>
-    <t>38.59350</t>
-  </si>
-  <si>
-    <t>-109.56866</t>
-  </si>
-  <si>
     <t>⏰ TIME UPDATED — ~2:40 PM → ~5:15 PM (added Hwy 95 + Hite Overlook scenic drive)</t>
   </si>
   <si>
@@ -2572,7 +2578,7 @@
     <t>What to Do / Notes</t>
   </si>
   <si>
-    <t>⚠️  MISSING STOPS — HIGH IMPACT</t>
+    <t>⚠️  עצירות חסרות — חשובות מאוד</t>
   </si>
   <si>
     <t>HIGH</t>
@@ -2582,7 +2588,7 @@
   </si>
   <si>
     <t xml:space="preserve">Day 4 or 5
-Fri May 8 / Sat May 9
+שישי 8 במאי / שבת 9 במאי
 (Cathedral Valley Inn)</t>
   </si>
   <si>
@@ -2590,54 +2596,54 @@
 Cathedral Valley</t>
   </si>
   <si>
-    <t>She sleeps 3 nights at Cathedral Valley Inn and has ZERO Cathedral Valley stops planned. A 400-ft isolated red monolith in Capitol Reef's north district. Almost nobody goes here.</t>
-  </si>
-  <si>
-    <t>Hartnet Road north from Caineville. Dirt road, OK when dry. All 3 Cathedral Valley sites in one 4-5 hr loop.</t>
+    <t>את ישנה 3 לילות ב-Cathedral Valley Inn ואין שום עצירה מתוכננת ב-Cathedral Valley. מונולית בודד של אבן חול אדומה בגובה 120 מטר בצפון Capitol Reef. כמעט אף אחד לא מגיע לכאן.</t>
+  </si>
+  <si>
+    <t>דרך Hartnet Road צפונה מ-Caineville. כביש עפר, עביר כשיבש. שלוש העצירות של Cathedral Valley באותה לולאה של 4-5 שעות.</t>
   </si>
   <si>
     <t xml:space="preserve">Day 4 or 5
-Fri May 8 / Sat May 9</t>
+שישי 8 במאי / שבת 9 במאי</t>
   </si>
   <si>
     <t xml:space="preserve">Temple of the Moon
 Cathedral Valley</t>
   </si>
   <si>
-    <t>Companion formation to Temple of the Sun on the same loop road.</t>
-  </si>
-  <si>
-    <t>Same Hartnet Road loop. Visit with Temple of Sun and Gypsum Sinkhole.</t>
+    <t>תצורה תאומה ל-Temple of the Sun באותה לולאת כביש.</t>
+  </si>
+  <si>
+    <t>באותה לולאה של Hartnet Road. לבקר יחד עם Temple of the Sun ו-Gypsum Sinkhole.</t>
   </si>
   <si>
     <t xml:space="preserve">Gypsum Sinkhole
 Cathedral Valley</t>
   </si>
   <si>
-    <t>A massive crater in the flat valley floor — very eerie and unusual.</t>
-  </si>
-  <si>
-    <t>On the same loop road as the Temples.</t>
-  </si>
-  <si>
-    <t>⚠️  ZION — DAYS 19 &amp; 20 HAVE NO CONTENT PLANNED</t>
+    <t>מכתש ענקי בקרקעית העמק השטוח — מאוד מוזר ומיוחד.</t>
+  </si>
+  <si>
+    <t>באותה לולאת כביש כמו ה-Temples.</t>
+  </si>
+  <si>
+    <t>⚠️  ZION — ימים 19 ו-20 ריקים מתוכן</t>
   </si>
   <si>
     <t>Fill Empty Day</t>
   </si>
   <si>
     <t xml:space="preserve">Day 19
-Sat May 23
+שבת 23 במאי
 (Zion)</t>
   </si>
   <si>
     <t>Angels Landing Trail</t>
   </si>
   <si>
-    <t>One of the most famous hikes in the US. Chains on the final section to a narrow summit ridge. Not in the itinerary at all.</t>
-  </si>
-  <si>
-    <t>Permit required — book at recreation.gov &gt; Zion NP &gt; Angels Landing. Alternative: Observation Point (no permit, even better view).</t>
+    <t>אחד המסלולים המפורסמים בעולם. שרשראות בקטע הסופי לרכס פסגה צר. בכלל לא מתוכנן.</t>
+  </si>
+  <si>
+    <t>דרוש היתר — להזמין ב-recreation.gov &gt; Zion NP &gt; Angels Landing. חלופה: Observation Point (בלי היתר, נוף אפילו טוב יותר).</t>
   </si>
   <si>
     <t xml:space="preserve">Day 19 or 20
@@ -2648,78 +2654,78 @@
 (Temple of Sinawava)</t>
   </si>
   <si>
-    <t>Walk up the Virgin River through slot canyon walls — unique experience. No permit needed.</t>
-  </si>
-  <si>
-    <t>Rent neoprene wetsuit in Springdale — May water is ~45°F cold. Take shuttle to last stop (Temple of Sinawava). Budget 4-6 hrs.</t>
+    <t>הליכה בנהר Virgin River בין קירות קניון צרים — חוויה ייחודית. בלי היתר.</t>
+  </si>
+  <si>
+    <t>לשכור wetsuit בספרינגדייל — מים במאי כ-7°C, קרים מאוד. שאטל לתחנה האחרונה (Temple of Sinawava). לתכנן 4-6 שעות.</t>
   </si>
   <si>
     <t xml:space="preserve">Day 20
-Sun May 24
+ראשון 24 במאי
 (Zion)</t>
   </si>
   <si>
     <t>Emerald Pools Trails</t>
   </si>
   <si>
-    <t>Three tiered pools with waterfalls. Beautiful and accessible. Not in the itinerary.</t>
-  </si>
-  <si>
-    <t>Lower Pool: Easy 0.6mi. Middle: 1.0mi. Upper: 1.2mi. Take shuttle to The Grotto stop.</t>
+    <t>שלוש בריכות מדורגות עם מפלים. יפהפה ונגיש. לא בתוכנית.</t>
+  </si>
+  <si>
+    <t>Lower Pool: קל 0.6 מייל. Middle: 1.0 מייל. Upper: 1.2 מייל. שאטל לתחנת The Grotto.</t>
   </si>
   <si>
     <t>MEDIUM</t>
   </si>
   <si>
     <t xml:space="preserve">Day 19
-Sat May 23
-(arriving via Hwy 9)</t>
+שבת 23 במאי
+(הגעה דרך Hwy 9)</t>
   </si>
   <si>
     <t>Canyon Overlook Trail</t>
   </si>
   <si>
-    <t>Short 1-mile trail to sweeping canyon view. Good warm-up. No shuttle needed.</t>
-  </si>
-  <si>
-    <t>Trailhead at east side of Zion-Mt Carmel Tunnel on Hwy 9.</t>
-  </si>
-  <si>
-    <t>🏨  SLEEPING CHANGES</t>
+    <t>מסלול קצר של מייל אחד עם תצפית מרהיבה על הקניון. חימום טוב. בלי שאטל.</t>
+  </si>
+  <si>
+    <t>טרילהד בצד המזרחי של מנהרת Zion-Mt Carmel ב-Hwy 9.</t>
+  </si>
+  <si>
+    <t>🏨  שינויי מלונות</t>
   </si>
   <si>
     <t>Sleeping Change</t>
   </si>
   <si>
     <t xml:space="preserve">Days 19–20
-May 23–24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANCEL Economy Inn &amp; Suites
-Book Springdale hotel instead</t>
-  </si>
-  <si>
-    <t>St. George is 45+ min from the Zion shuttle. Springdale is 5 minutes — enables early start for Angels Landing and full day in the canyon.</t>
-  </si>
-  <si>
-    <t>Hampton Inn Springdale or similar. Essential if Angels Landing permit is obtained (must start by 7am).</t>
+23-24 במאי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">לבטל Economy Inn &amp; Suites
+ולהזמין מלון בספרינגדייל במקום</t>
+  </si>
+  <si>
+    <t>St. George במרחק 45+ דקות מהשאטל של Zion. ספרינגדייל במרחק 5 דקות — מאפשר התחלה מוקדמת ל-Angels Landing ויום מלא בקניון.</t>
+  </si>
+  <si>
+    <t>Hampton Inn Springdale או דומה. הכרחי אם משיגים היתר ל-Angels Landing (חייבים להתחיל עד 7:00).</t>
   </si>
   <si>
     <t xml:space="preserve">Day 14 area
-Mon May 18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optional: Add Monument Valley night
+שני 18 במאי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אופציונלי: להוסיף לילה ב-Monument Valley
 (The View Hotel)</t>
   </si>
   <si>
-    <t>The iconic Mittens photo requires golden hour light. Arriving midday gives flat harsh light.</t>
-  </si>
-  <si>
-    <t>The View Hotel (Navajo Nation) on the canyon rim. Book far in advance. At minimum arrive by 6pm for golden hour.</t>
-  </si>
-  <si>
-    <t>🔧  DATA ERRORS — Fix or Remove Before the Trip</t>
+    <t>התמונה האייקונית של ה-Mittens דורשת אור של שעת זהב. הגעה בצהריים נותנת אור שטוח וחזק.</t>
+  </si>
+  <si>
+    <t>The View Hotel (שמורת Navajo) על שפת הקניון. להזמין הרבה זמן מראש. לפחות להגיע עד 18:00 בערב לתפיסת שעת הזהב.</t>
+  </si>
+  <si>
+    <t>🔧  שגיאות בנתונים — לתקן או להסיר לפני הטיול</t>
   </si>
   <si>
     <t>FIX</t>
@@ -2728,40 +2734,40 @@
     <t>Remove</t>
   </si>
   <si>
-    <t>Day 5 — Sat May 9</t>
-  </si>
-  <si>
-    <t>REMOVE: Cosmic Ash Hills Walk Utah</t>
-  </si>
-  <si>
-    <t>No such trail exists anywhere.</t>
-  </si>
-  <si>
-    <t>Remove from itinerary.</t>
+    <t>Day 5 — שבת 9 במאי</t>
+  </si>
+  <si>
+    <t>להסיר: Cosmic Ash Hills Walk Utah</t>
+  </si>
+  <si>
+    <t>מסלול כזה לא קיים בשום מקום.</t>
+  </si>
+  <si>
+    <t>להסיר מהמסלול.</t>
   </si>
   <si>
     <t>Fix Coords</t>
   </si>
   <si>
-    <t>FIX: Rainbow Hills Loop — wrong coordinates</t>
-  </si>
-  <si>
-    <t>Coordinates are ~80 miles off (pointing near St. George).</t>
-  </si>
-  <si>
-    <t>Ask mom to find the article she read — need to verify exact location.</t>
-  </si>
-  <si>
-    <t>Day 6 — Sun May 10</t>
-  </si>
-  <si>
-    <t>FIX: Carmel Canyon Loop Utah</t>
-  </si>
-  <si>
-    <t>Coordinates point to St. George — 170 miles off. Will break navigation.</t>
-  </si>
-  <si>
-    <t>Correct coordinates: approx (38.570, -110.710) in Goblin Valley.</t>
+    <t>לתקן: קואורדינטות שגויות ב-Rainbow Hills Loop</t>
+  </si>
+  <si>
+    <t>הקואורדינטות מוטעות בכ-130 ק"מ (מצביעות ליד St. George).</t>
+  </si>
+  <si>
+    <t>לבקש מאמא למצוא את הכתבה שקראה — צריך לאמת את המיקום המדויק.</t>
+  </si>
+  <si>
+    <t>Day 6 — ראשון 10 במאי</t>
+  </si>
+  <si>
+    <t>לתקן: Carmel Canyon Loop Utah</t>
+  </si>
+  <si>
+    <t>הקואורדינטות מצביעות ל-St. George — 270 ק"מ הרחק. ישבור את הניווט.</t>
+  </si>
+  <si>
+    <t>קואורדינטות נכונות: בערך (38.570, -110.710) ב-Goblin Valley.</t>
   </si>
   <si>
     <t>DONE</t>
@@ -2770,65 +2776,65 @@
     <t>Removed</t>
   </si>
   <si>
-    <t>Day 21 — Mon May 25</t>
-  </si>
-  <si>
-    <t>REMOVED: Petrified Logs Kanarra Falls</t>
-  </si>
-  <si>
-    <t>Petrified logs are real — but they are at Escalante Petrified Forest State Park, not at Kanarra Falls. ChatGPT confused two places.</t>
-  </si>
-  <si>
-    <t>✅ Removed from itinerary 2026-05-01. Petrified logs not visited on this trip.</t>
-  </si>
-  <si>
-    <t>REMOVED: Seven Wonders Kanarra Falls</t>
-  </si>
-  <si>
-    <t>Seven Wonders is a real loop — but it is at Valley of Fire (near the Fire Wave trailhead), not at Kanarra Falls.</t>
-  </si>
-  <si>
-    <t>✅ Removed from itinerary 2026-05-01. The Fire Wave stop on Day 21 already passes through this area — no plan change needed, just renamed correctly.</t>
+    <t>Day 21 — שני 25 במאי</t>
+  </si>
+  <si>
+    <t>הוסר: Petrified Logs Kanarra Falls</t>
+  </si>
+  <si>
+    <t>Petrified Logs קיימים — אבל ב-Escalante Petrified Forest State Park, לא ב-Kanarra Falls. ChatGPT בלבל בין שני מקומות.</t>
+  </si>
+  <si>
+    <t>✅ הוסר מהמסלול ב-2026-05-01. Petrified Logs לא יבוקרו בטיול הזה.</t>
+  </si>
+  <si>
+    <t>הוסר: Seven Wonders Kanarra Falls</t>
+  </si>
+  <si>
+    <t>Seven Wonders הוא מסלול אמיתי — אבל ב-Valley of Fire (ליד טרילהד Fire Wave), לא ב-Kanarra Falls.</t>
+  </si>
+  <si>
+    <t>✅ הוסר מהמסלול ב-2026-05-01. עצירת Fire Wave ביום 21 כבר עוברת באזור הזה — אין צורך בשינוי תוכנית, רק שינוי שם.</t>
   </si>
   <si>
     <t>Renamed</t>
   </si>
   <si>
-    <t xml:space="preserve">RENAMED: Elephant Rock — Valley of Fire
-(was: "Elephant Rock Kanarra Falls")</t>
-  </si>
-  <si>
-    <t>Elephant Rock is at Valley of Fire, not Kanarra Falls. The old name confused two places.</t>
-  </si>
-  <si>
-    <t>✅ Renamed 2026-05-01. Mom passes Elephant Rock visible from the road at 3:00 PM driving from Atlatl Rock to Fire Wave.</t>
+    <t xml:space="preserve">שונה שם: Elephant Rock — Valley of Fire
+(היה: "Elephant Rock Kanarra Falls")</t>
+  </si>
+  <si>
+    <t>Elephant Rock נמצא ב-Valley of Fire, לא ב-Kanarra Falls. השם הישן בלבל בין שני מקומות.</t>
+  </si>
+  <si>
+    <t>✅ שונה ב-2026-05-01. אמא עוברת על-יד Elephant Rock שנראה מהכביש בשעה 15:00 בנסיעה מ-Atlatl Rock ל-Fire Wave.</t>
   </si>
   <si>
     <t>Add Coords</t>
   </si>
   <si>
-    <t>Day 15 — Tue May 19</t>
-  </si>
-  <si>
-    <t>FIX: Spencer Trail — add coordinates</t>
-  </si>
-  <si>
-    <t>Real and worthwhile hike at Lees Ferry. Coordinates just missing.</t>
-  </si>
-  <si>
-    <t>Spencer Trail trailhead coordinates: (36.864, -111.586). 3.5 mile round trip.</t>
-  </si>
-  <si>
-    <t>Day 12 — Sat May 16</t>
-  </si>
-  <si>
-    <t>FIX: Devil's Garden Hoodoos Utah</t>
-  </si>
-  <si>
-    <t>Coordinates point to Arches National Park. The Escalante Devil's Garden is a completely different place.</t>
-  </si>
-  <si>
-    <t>Correct coordinates near Escalante: approx (37.787, -111.396).</t>
+    <t>Day 15 — שלישי 19 במאי</t>
+  </si>
+  <si>
+    <t>לתקן: Spencer Trail — להוסיף קואורדינטות</t>
+  </si>
+  <si>
+    <t>מסלול אמיתי וכדאי ב-Lees Ferry. הקואורדינטות פשוט חסרות.</t>
+  </si>
+  <si>
+    <t>קואורדינטות טרילהד Spencer Trail: (36.864, -111.586). 3.5 מייל הלוך-חזור.</t>
+  </si>
+  <si>
+    <t>Day 12 — שבת 16 במאי</t>
+  </si>
+  <si>
+    <t>לתקן: Devil's Garden Hoodoos Utah</t>
+  </si>
+  <si>
+    <t>הקואורדינטות מצביעות ל-Arches National Park. ה-Devil's Garden של Escalante הוא מקום אחר לחלוטין.</t>
+  </si>
+  <si>
+    <t>קואורדינטות נכונות ליד Escalante: בערך (37.787, -111.396).</t>
   </si>
   <si>
     <t>Daily Guide — Activity Color Key</t>
@@ -3948,10 +3954,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G5" s="15" t="s">
         <v>14</v>
@@ -3962,22 +3968,22 @@
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G6" s="21" t="s">
         <v>14</v>
@@ -4014,7 +4020,7 @@
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -4026,16 +4032,16 @@
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>14</v>
@@ -4052,22 +4058,22 @@
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G10" s="28" t="s">
         <v>14</v>
@@ -4078,22 +4084,22 @@
     </row>
     <row r="11" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G11" s="34" t="s">
         <v>14</v>
@@ -4104,16 +4110,16 @@
     </row>
     <row r="12" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E12" s="14" t="s">
         <v>14</v>
@@ -4130,22 +4136,22 @@
     </row>
     <row r="13" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="23" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G13" s="28" t="s">
         <v>14</v>
@@ -4156,22 +4162,22 @@
     </row>
     <row r="14" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="35" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G14" s="40" t="s">
         <v>14</v>
@@ -4182,16 +4188,16 @@
     </row>
     <row r="15" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="35" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E15" s="39" t="s">
         <v>14</v>
@@ -4208,22 +4214,22 @@
     </row>
     <row r="16" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F16" s="33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G16" s="34" t="s">
         <v>14</v>
@@ -4234,22 +4240,22 @@
     </row>
     <row r="17" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="23" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G17" s="28" t="s">
         <v>14</v>
@@ -4260,22 +4266,22 @@
     </row>
     <row r="18" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F18" s="27" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G18" s="28" t="s">
         <v>14</v>
@@ -4286,80 +4292,80 @@
     </row>
     <row r="19" ht="100" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="35" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B19" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C19" s="37" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D19" s="38" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G19" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H19" s="41" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" ht="118" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F20" s="33" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G20" s="34" t="s">
         <v>14</v>
       </c>
       <c r="H20" s="41" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D21" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G21" s="21" t="s">
         <v>14</v>
       </c>
       <c r="H21" s="41" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" ht="8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4390,7 +4396,7 @@
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -4402,16 +4408,16 @@
     </row>
     <row r="24" ht="82" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E24" s="14" t="s">
         <v>14</v>
@@ -4423,47 +4429,47 @@
         <v>14</v>
       </c>
       <c r="H24" s="41" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" ht="136" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="29" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C25" s="31" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D25" s="32" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F25" s="33" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G25" s="34" t="s">
         <v>14</v>
       </c>
       <c r="H25" s="41" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E26" s="14" t="s">
         <v>14</v>
@@ -4475,47 +4481,47 @@
         <v>14</v>
       </c>
       <c r="H26" s="41" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="23" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G27" s="28" t="s">
         <v>14</v>
       </c>
       <c r="H27" s="41" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E28" s="14" t="s">
         <v>14</v>
@@ -4527,73 +4533,73 @@
         <v>14</v>
       </c>
       <c r="H28" s="41" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="23" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G29" s="28" t="s">
         <v>14</v>
       </c>
       <c r="H29" s="41" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="23" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E30" s="27" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F30" s="27" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G30" s="28" t="s">
         <v>14</v>
       </c>
       <c r="H30" s="41" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E31" s="14" t="s">
         <v>14</v>
@@ -4605,47 +4611,47 @@
         <v>14</v>
       </c>
       <c r="H31" s="41" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="35" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C32" s="37" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E32" s="39" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F32" s="39" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G32" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H32" s="41" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="35" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D33" s="38" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E33" s="39" t="s">
         <v>14</v>
@@ -4657,21 +4663,21 @@
         <v>14</v>
       </c>
       <c r="H33" s="41" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E34" s="14" t="s">
         <v>14</v>
@@ -4683,85 +4689,85 @@
         <v>14</v>
       </c>
       <c r="H34" s="41" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="35" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C35" s="37" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D35" s="38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E35" s="39" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F35" s="39" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G35" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H35" s="41" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="23" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E36" s="27" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F36" s="27" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G36" s="28" t="s">
         <v>14</v>
       </c>
       <c r="H36" s="41" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="37" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="23" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F37" s="27" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G37" s="28" t="s">
         <v>14</v>
       </c>
       <c r="H37" s="41" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" ht="82" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4772,7 +4778,7 @@
         <v>11</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>14</v>
@@ -4792,42 +4798,42 @@
     </row>
     <row r="39" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="35" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E39" s="39" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F39" s="39" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G39" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H39" s="41" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="40" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B40" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E40" s="14" t="s">
         <v>14</v>
@@ -4839,33 +4845,33 @@
         <v>14</v>
       </c>
       <c r="H40" s="41" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="41" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D41" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G41" s="21" t="s">
         <v>14</v>
       </c>
       <c r="H41" s="41" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="42" ht="8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4896,7 +4902,7 @@
     </row>
     <row r="43" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -4908,16 +4914,16 @@
     </row>
     <row r="44" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E44" s="14" t="s">
         <v>14</v>
@@ -4934,22 +4940,22 @@
     </row>
     <row r="45" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="35" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E45" s="39" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F45" s="39" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G45" s="40" t="s">
         <v>14</v>
@@ -4963,19 +4969,19 @@
         <v>10</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D46" s="26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E46" s="27" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F46" s="27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G46" s="28" t="s">
         <v>14</v>
@@ -4986,22 +4992,22 @@
     </row>
     <row r="47" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="29" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B47" s="30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C47" s="31" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D47" s="32" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E47" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F47" s="33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G47" s="34" t="s">
         <v>14</v>
@@ -5012,16 +5018,16 @@
     </row>
     <row r="48" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E48" s="14" t="s">
         <v>14</v>
@@ -5038,28 +5044,28 @@
     </row>
     <row r="49" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D49" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G49" s="21" t="s">
         <v>14</v>
       </c>
       <c r="H49" s="41" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="50" ht="8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5090,7 +5096,7 @@
     </row>
     <row r="51" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -5102,16 +5108,16 @@
     </row>
     <row r="52" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E52" s="14" t="s">
         <v>14</v>
@@ -5128,16 +5134,16 @@
     </row>
     <row r="53" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="29" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B53" s="30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C53" s="31" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D53" s="32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E53" s="33" t="s">
         <v>14</v>
@@ -5154,16 +5160,16 @@
     </row>
     <row r="54" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="35" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C54" s="37" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D54" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E54" s="39" t="s">
         <v>14</v>
@@ -5180,16 +5186,16 @@
     </row>
     <row r="55" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="35" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C55" s="37" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D55" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E55" s="39" t="s">
         <v>14</v>
@@ -5206,16 +5212,16 @@
     </row>
     <row r="56" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E56" s="14" t="s">
         <v>14</v>
@@ -5232,22 +5238,22 @@
     </row>
     <row r="57" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B57" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C57" s="25" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D57" s="26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E57" s="27" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F57" s="27" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G57" s="28" t="s">
         <v>14</v>
@@ -5258,22 +5264,22 @@
     </row>
     <row r="58" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C58" s="37" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D58" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E58" s="39" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F58" s="39" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="G58" s="40" t="s">
         <v>14</v>
@@ -5284,16 +5290,16 @@
     </row>
     <row r="59" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E59" s="14" t="s">
         <v>14</v>
@@ -5310,22 +5316,22 @@
     </row>
     <row r="60" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G60" s="15" t="s">
         <v>14</v>
@@ -5336,22 +5342,22 @@
     </row>
     <row r="61" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="23" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B61" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C61" s="25" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D61" s="26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E61" s="27" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F61" s="27" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G61" s="28" t="s">
         <v>14</v>
@@ -5362,22 +5368,22 @@
     </row>
     <row r="62" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="23" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B62" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C62" s="25" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D62" s="26" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E62" s="27" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F62" s="27" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G62" s="28" t="s">
         <v>14</v>
@@ -5388,22 +5394,22 @@
     </row>
     <row r="63" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="23" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B63" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C63" s="25" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D63" s="26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E63" s="27" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F63" s="27" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G63" s="28" t="s">
         <v>14</v>
@@ -5414,22 +5420,22 @@
     </row>
     <row r="64" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="G64" s="15" t="s">
         <v>14</v>
@@ -5440,22 +5446,22 @@
     </row>
     <row r="65" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="35" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C65" s="37" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D65" s="38" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="E65" s="39" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F65" s="39" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="G65" s="40" t="s">
         <v>14</v>
@@ -5466,16 +5472,16 @@
     </row>
     <row r="66" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E66" s="14" t="s">
         <v>14</v>
@@ -5487,73 +5493,73 @@
         <v>14</v>
       </c>
       <c r="H66" s="41" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="67" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="23" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B67" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C67" s="25" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D67" s="26" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E67" s="27" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F67" s="27" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G67" s="28" t="s">
         <v>14</v>
       </c>
       <c r="H67" s="41" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="68" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="G68" s="15" t="s">
         <v>14</v>
       </c>
       <c r="H68" s="41" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="69" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="23" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B69" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C69" s="25" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D69" s="26" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E69" s="27" t="s">
         <v>14</v>
@@ -5565,21 +5571,21 @@
         <v>14</v>
       </c>
       <c r="H69" s="41" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="70" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E70" s="14" t="s">
         <v>14</v>
@@ -5591,33 +5597,33 @@
         <v>14</v>
       </c>
       <c r="H70" s="41" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="71" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="16" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D71" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E71" s="20" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="F71" s="20" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="G71" s="21" t="s">
         <v>14</v>
       </c>
       <c r="H71" s="41" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="72" ht="8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5648,7 +5654,7 @@
     </row>
     <row r="73" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -5660,16 +5666,16 @@
     </row>
     <row r="74" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E74" s="14" t="s">
         <v>14</v>
@@ -5686,22 +5692,22 @@
     </row>
     <row r="75" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="35" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B75" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C75" s="37" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D75" s="38" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E75" s="39" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F75" s="39" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="G75" s="40" t="s">
         <v>14</v>
@@ -5712,22 +5718,22 @@
     </row>
     <row r="76" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="35" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B76" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C76" s="37" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D76" s="38" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E76" s="39" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F76" s="39" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="G76" s="40" t="s">
         <v>14</v>
@@ -5738,22 +5744,22 @@
     </row>
     <row r="77" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="35" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B77" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C77" s="37" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D77" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E77" s="39" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F77" s="39" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G77" s="40" t="s">
         <v>14</v>
@@ -5764,22 +5770,22 @@
     </row>
     <row r="78" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="35" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B78" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C78" s="37" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D78" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E78" s="39" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="F78" s="39" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="G78" s="40" t="s">
         <v>14</v>
@@ -5790,22 +5796,22 @@
     </row>
     <row r="79" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="35" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B79" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C79" s="37" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D79" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E79" s="39" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F79" s="39" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="G79" s="40" t="s">
         <v>14</v>
@@ -5816,22 +5822,22 @@
     </row>
     <row r="80" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="35" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B80" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C80" s="37" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D80" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E80" s="39" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="F80" s="39" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="G80" s="40" t="s">
         <v>14</v>
@@ -5842,68 +5848,68 @@
     </row>
     <row r="81" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G81" s="9" t="s">
         <v>14</v>
       </c>
       <c r="H81" s="41" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="82" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="35" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B82" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C82" s="37" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D82" s="38" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E82" s="39" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F82" s="39" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G82" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H82" s="41" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="83" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="10" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B83" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E83" s="14" t="s">
         <v>14</v>
@@ -5920,28 +5926,28 @@
     </row>
     <row r="84" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="16" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C84" s="18" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D84" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E84" s="20" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F84" s="20" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G84" s="21" t="s">
         <v>14</v>
       </c>
       <c r="H84" s="41" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="85" ht="8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5972,7 +5978,7 @@
     </row>
     <row r="86" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -5984,16 +5990,16 @@
     </row>
     <row r="87" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B87" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E87" s="14" t="s">
         <v>14</v>
@@ -6010,22 +6016,22 @@
     </row>
     <row r="88" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="35" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B88" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C88" s="37" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D88" s="38" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E88" s="39" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="F88" s="39" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G88" s="40" t="s">
         <v>14</v>
@@ -6036,22 +6042,22 @@
     </row>
     <row r="89" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="35" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B89" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C89" s="37" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D89" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E89" s="39" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F89" s="39" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="G89" s="40" t="s">
         <v>14</v>
@@ -6062,22 +6068,22 @@
     </row>
     <row r="90" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="29" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B90" s="30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C90" s="31" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D90" s="32" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E90" s="33" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F90" s="33" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="G90" s="34" t="s">
         <v>14</v>
@@ -6088,16 +6094,16 @@
     </row>
     <row r="91" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="10" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B91" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D91" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E91" s="14" t="s">
         <v>14</v>
@@ -6114,22 +6120,22 @@
     </row>
     <row r="92" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="23" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B92" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C92" s="25" t="s">
+        <v>306</v>
+      </c>
+      <c r="D92" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C92" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="D92" s="26" t="s">
-        <v>27</v>
-      </c>
       <c r="E92" s="27" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F92" s="27" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G92" s="28" t="s">
         <v>14</v>
@@ -6140,16 +6146,16 @@
     </row>
     <row r="93" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="10" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B93" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D93" s="13" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E93" s="14" t="s">
         <v>14</v>
@@ -6161,47 +6167,47 @@
         <v>14</v>
       </c>
       <c r="H93" s="41" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="94" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="23" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B94" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C94" s="25" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D94" s="26" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E94" s="27" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F94" s="27" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="G94" s="28" t="s">
         <v>14</v>
       </c>
       <c r="H94" s="41" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="95" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="10" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B95" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D95" s="13" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E95" s="14" t="s">
         <v>14</v>
@@ -6213,33 +6219,33 @@
         <v>14</v>
       </c>
       <c r="H95" s="41" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="96" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="16" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C96" s="18" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D96" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E96" s="20" t="s">
-        <v>317</v>
+        <v>286</v>
       </c>
       <c r="F96" s="20" t="s">
-        <v>318</v>
+        <v>287</v>
       </c>
       <c r="G96" s="21" t="s">
         <v>14</v>
       </c>
       <c r="H96" s="41" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="97" ht="8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6270,7 +6276,7 @@
     </row>
     <row r="98" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -6282,16 +6288,16 @@
     </row>
     <row r="99" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="10" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B99" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D99" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E99" s="14" t="s">
         <v>14</v>
@@ -6308,22 +6314,22 @@
     </row>
     <row r="100" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="29" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B100" s="30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C100" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D100" s="32" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E100" s="33" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F100" s="33" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G100" s="34" t="s">
         <v>14</v>
@@ -6334,16 +6340,16 @@
     </row>
     <row r="101" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="10" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B101" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D101" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E101" s="14" t="s">
         <v>14</v>
@@ -6360,22 +6366,22 @@
     </row>
     <row r="102" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="35" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B102" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C102" s="37" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D102" s="38" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E102" s="39" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F102" s="39" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G102" s="40" t="s">
         <v>14</v>
@@ -6386,22 +6392,22 @@
     </row>
     <row r="103" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="23" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B103" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C103" s="25" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D103" s="26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E103" s="27" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F103" s="27" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G103" s="28" t="s">
         <v>14</v>
@@ -6412,16 +6418,16 @@
     </row>
     <row r="104" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B104" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D104" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E104" s="14" t="s">
         <v>14</v>
@@ -6438,16 +6444,16 @@
     </row>
     <row r="105" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E105" s="8" t="s">
         <v>14</v>
@@ -6464,16 +6470,16 @@
     </row>
     <row r="106" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="10" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B106" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D106" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E106" s="14" t="s">
         <v>14</v>
@@ -6490,22 +6496,22 @@
     </row>
     <row r="107" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="35" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B107" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C107" s="37" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D107" s="38" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E107" s="39" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F107" s="39" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="G107" s="40" t="s">
         <v>14</v>
@@ -6516,16 +6522,16 @@
     </row>
     <row r="108" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B108" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D108" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E108" s="14" t="s">
         <v>14</v>
@@ -6542,22 +6548,22 @@
     </row>
     <row r="109" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="35" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B109" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C109" s="37" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D109" s="38" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E109" s="39" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F109" s="39" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G109" s="40" t="s">
         <v>14</v>
@@ -6568,16 +6574,16 @@
     </row>
     <row r="110" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="10" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B110" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D110" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E110" s="14" t="s">
         <v>14</v>
@@ -6594,16 +6600,16 @@
     </row>
     <row r="111" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E111" s="8" t="s">
         <v>14</v>
@@ -6620,22 +6626,22 @@
     </row>
     <row r="112" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="23" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B112" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C112" s="25" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D112" s="26" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E112" s="27" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F112" s="27" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G112" s="28" t="s">
         <v>14</v>
@@ -6646,16 +6652,16 @@
     </row>
     <row r="113" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="10" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B113" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D113" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E113" s="14" t="s">
         <v>14</v>
@@ -6672,22 +6678,22 @@
     </row>
     <row r="114" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="16" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B114" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C114" s="18" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D114" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E114" s="20" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F114" s="20" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G114" s="21" t="s">
         <v>14</v>
@@ -6724,7 +6730,7 @@
     </row>
     <row r="116" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -6736,16 +6742,16 @@
     </row>
     <row r="117" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B117" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D117" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E117" s="14" t="s">
         <v>14</v>
@@ -6762,22 +6768,22 @@
     </row>
     <row r="118" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="35" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B118" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C118" s="37" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D118" s="38" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E118" s="39" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F118" s="39" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G118" s="40" t="s">
         <v>14</v>
@@ -6788,22 +6794,22 @@
     </row>
     <row r="119" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B119" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D119" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E119" s="14" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F119" s="14" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G119" s="15" t="s">
         <v>14</v>
@@ -6814,22 +6820,22 @@
     </row>
     <row r="120" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="35" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B120" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C120" s="37" t="s">
+        <v>373</v>
+      </c>
+      <c r="D120" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="E120" s="39" t="s">
         <v>371</v>
       </c>
-      <c r="D120" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="E120" s="39" t="s">
-        <v>369</v>
-      </c>
       <c r="F120" s="39" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G120" s="40" t="s">
         <v>14</v>
@@ -6840,22 +6846,22 @@
     </row>
     <row r="121" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="35" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B121" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C121" s="37" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D121" s="38" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E121" s="39" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F121" s="39" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G121" s="40" t="s">
         <v>14</v>
@@ -6866,16 +6872,16 @@
     </row>
     <row r="122" ht="82" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="42" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C122" s="43" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D122" s="44" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E122" s="45" t="s">
         <v>14</v>
@@ -6884,7 +6890,7 @@
         <v>14</v>
       </c>
       <c r="G122" s="46" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H122" s="47" t="s">
         <v>14</v>
@@ -6892,16 +6898,16 @@
     </row>
     <row r="123" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="10" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B123" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D123" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E123" s="14" t="s">
         <v>14</v>
@@ -6918,22 +6924,22 @@
     </row>
     <row r="124" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="35" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B124" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C124" s="37" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D124" s="38" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E124" s="39" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F124" s="39" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G124" s="40" t="s">
         <v>14</v>
@@ -6944,16 +6950,16 @@
     </row>
     <row r="125" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="10" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B125" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D125" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E125" s="14" t="s">
         <v>14</v>
@@ -6970,22 +6976,22 @@
     </row>
     <row r="126" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="16" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B126" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C126" s="18" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D126" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E126" s="20" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F126" s="20" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G126" s="21" t="s">
         <v>14</v>
@@ -7022,7 +7028,7 @@
     </row>
     <row r="128" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -7034,16 +7040,16 @@
     </row>
     <row r="129" ht="154" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="48" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B129" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C129" s="49" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D129" s="50" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E129" s="51" t="s">
         <v>14</v>
@@ -7052,7 +7058,7 @@
         <v>14</v>
       </c>
       <c r="G129" s="52" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H129" s="53" t="s">
         <v>14</v>
@@ -7060,22 +7066,22 @@
     </row>
     <row r="130" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="35" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B130" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C130" s="37" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D130" s="38" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E130" s="39" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F130" s="39" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G130" s="40" t="s">
         <v>14</v>
@@ -7086,16 +7092,16 @@
     </row>
     <row r="131" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="10" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B131" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D131" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E131" s="14" t="s">
         <v>14</v>
@@ -7112,22 +7118,22 @@
     </row>
     <row r="132" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="35" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B132" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C132" s="37" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D132" s="38" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E132" s="39" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F132" s="39" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="G132" s="40" t="s">
         <v>14</v>
@@ -7138,22 +7144,22 @@
     </row>
     <row r="133" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="29" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B133" s="30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C133" s="31" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D133" s="32" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E133" s="33" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F133" s="33" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="G133" s="34" t="s">
         <v>14</v>
@@ -7164,22 +7170,22 @@
     </row>
     <row r="134" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="10" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B134" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D134" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E134" s="14" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F134" s="14" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G134" s="15" t="s">
         <v>14</v>
@@ -7190,22 +7196,22 @@
     </row>
     <row r="135" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="29" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B135" s="30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C135" s="31" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D135" s="32" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E135" s="33" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F135" s="33" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="G135" s="34" t="s">
         <v>14</v>
@@ -7216,25 +7222,25 @@
     </row>
     <row r="136" ht="208" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="42" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B136" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C136" s="43" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D136" s="44" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E136" s="45" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F136" s="45" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G136" s="46" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H136" s="47" t="s">
         <v>14</v>
@@ -7242,16 +7248,16 @@
     </row>
     <row r="137" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="10" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B137" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D137" s="13" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E137" s="14" t="s">
         <v>14</v>
@@ -7268,22 +7274,22 @@
     </row>
     <row r="138" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="16" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C138" s="18" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D138" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E138" s="20" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F138" s="20" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G138" s="21" t="s">
         <v>14</v>
@@ -7320,7 +7326,7 @@
     </row>
     <row r="140" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -7332,16 +7338,16 @@
     </row>
     <row r="141" ht="496" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="42" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B141" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C141" s="43" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D141" s="44" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E141" s="45" t="s">
         <v>14</v>
@@ -7350,7 +7356,7 @@
         <v>14</v>
       </c>
       <c r="G141" s="46" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H141" s="47" t="s">
         <v>14</v>
@@ -7358,22 +7364,22 @@
     </row>
     <row r="142" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="35" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B142" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C142" s="37" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D142" s="38" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E142" s="39" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F142" s="39" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G142" s="40" t="s">
         <v>14</v>
@@ -7384,16 +7390,16 @@
     </row>
     <row r="143" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="10" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B143" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D143" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E143" s="14" t="s">
         <v>14</v>
@@ -7410,22 +7416,22 @@
     </row>
     <row r="144" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="29" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B144" s="30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C144" s="31" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D144" s="32" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E144" s="33" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F144" s="33" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="G144" s="34" t="s">
         <v>14</v>
@@ -7436,22 +7442,22 @@
     </row>
     <row r="145" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D145" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G145" s="9" t="s">
         <v>14</v>
@@ -7462,16 +7468,16 @@
     </row>
     <row r="146" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="10" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B146" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D146" s="13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E146" s="14" t="s">
         <v>14</v>
@@ -7488,22 +7494,22 @@
     </row>
     <row r="147" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="23" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B147" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C147" s="25" t="s">
+        <v>445</v>
+      </c>
+      <c r="D147" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C147" s="25" t="s">
-        <v>443</v>
-      </c>
-      <c r="D147" s="26" t="s">
-        <v>27</v>
-      </c>
       <c r="E147" s="27" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F147" s="27" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="G147" s="28" t="s">
         <v>14</v>
@@ -7514,22 +7520,22 @@
     </row>
     <row r="148" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="23" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B148" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C148" s="25" t="s">
+        <v>449</v>
+      </c>
+      <c r="D148" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C148" s="25" t="s">
-        <v>447</v>
-      </c>
-      <c r="D148" s="26" t="s">
-        <v>27</v>
-      </c>
       <c r="E148" s="27" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F148" s="27" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="G148" s="28" t="s">
         <v>14</v>
@@ -7540,16 +7546,16 @@
     </row>
     <row r="149" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="10" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B149" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D149" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E149" s="14" t="s">
         <v>14</v>
@@ -7566,22 +7572,22 @@
     </row>
     <row r="150" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="35" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B150" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C150" s="37" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D150" s="38" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E150" s="39" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F150" s="39" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="G150" s="40" t="s">
         <v>14</v>
@@ -7592,16 +7598,16 @@
     </row>
     <row r="151" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="10" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B151" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D151" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E151" s="14" t="s">
         <v>14</v>
@@ -7618,22 +7624,22 @@
     </row>
     <row r="152" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="16" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B152" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C152" s="18" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D152" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E152" s="20" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F152" s="20" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="G152" s="21" t="s">
         <v>14</v>
@@ -7670,7 +7676,7 @@
     </row>
     <row r="154" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -7682,16 +7688,16 @@
     </row>
     <row r="155" ht="532" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="42" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B155" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C155" s="43" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D155" s="44" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E155" s="45" t="s">
         <v>14</v>
@@ -7700,7 +7706,7 @@
         <v>14</v>
       </c>
       <c r="G155" s="46" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="H155" s="47" t="s">
         <v>14</v>
@@ -7708,22 +7714,22 @@
     </row>
     <row r="156" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="23" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B156" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C156" s="25" t="s">
+        <v>468</v>
+      </c>
+      <c r="D156" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C156" s="25" t="s">
-        <v>466</v>
-      </c>
-      <c r="D156" s="26" t="s">
-        <v>27</v>
-      </c>
       <c r="E156" s="27" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F156" s="27" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="G156" s="28" t="s">
         <v>14</v>
@@ -7734,22 +7740,22 @@
     </row>
     <row r="157" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="10" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B157" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C157" s="12" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D157" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E157" s="14" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F157" s="14" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="G157" s="15" t="s">
         <v>14</v>
@@ -7760,22 +7766,22 @@
     </row>
     <row r="158" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="23" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B158" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C158" s="25" t="s">
+        <v>476</v>
+      </c>
+      <c r="D158" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C158" s="25" t="s">
-        <v>474</v>
-      </c>
-      <c r="D158" s="26" t="s">
-        <v>27</v>
-      </c>
       <c r="E158" s="27" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F158" s="27" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="G158" s="28" t="s">
         <v>14</v>
@@ -7786,22 +7792,22 @@
     </row>
     <row r="159" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="29" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B159" s="30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C159" s="31" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D159" s="32" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E159" s="33" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F159" s="33" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="G159" s="34" t="s">
         <v>14</v>
@@ -7812,16 +7818,16 @@
     </row>
     <row r="160" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="10" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B160" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C160" s="12" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D160" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E160" s="14" t="s">
         <v>14</v>
@@ -7838,22 +7844,22 @@
     </row>
     <row r="161" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="23" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B161" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C161" s="25" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D161" s="26" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E161" s="27" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="F161" s="27" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="G161" s="28" t="s">
         <v>14</v>
@@ -7864,22 +7870,22 @@
     </row>
     <row r="162" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="35" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B162" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C162" s="37" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D162" s="38" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E162" s="39" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F162" s="39" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="G162" s="40" t="s">
         <v>14</v>
@@ -7890,22 +7896,22 @@
     </row>
     <row r="163" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="35" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B163" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C163" s="37" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D163" s="38" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E163" s="39" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F163" s="39" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="G163" s="40" t="s">
         <v>14</v>
@@ -7916,22 +7922,22 @@
     </row>
     <row r="164" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="35" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B164" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C164" s="37" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D164" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E164" s="39" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F164" s="39" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="G164" s="40" t="s">
         <v>14</v>
@@ -7942,80 +7948,80 @@
     </row>
     <row r="165" ht="82" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="29" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B165" s="30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C165" s="31" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D165" s="32" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E165" s="33" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F165" s="33" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="G165" s="34" t="s">
         <v>14</v>
       </c>
       <c r="H165" s="41" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="166" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="23" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B166" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C166" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="D166" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C166" s="25" t="s">
-        <v>499</v>
-      </c>
-      <c r="D166" s="26" t="s">
-        <v>27</v>
-      </c>
       <c r="E166" s="27" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F166" s="27" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="G166" s="28" t="s">
         <v>14</v>
       </c>
       <c r="H166" s="41" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="167" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B167" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C167" s="18" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D167" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E167" s="20" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="F167" s="20" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="G167" s="21" t="s">
         <v>14</v>
       </c>
       <c r="H167" s="41" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="168" ht="8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8046,7 +8052,7 @@
     </row>
     <row r="169" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -8058,16 +8064,16 @@
     </row>
     <row r="170" ht="442" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="42" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B170" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C170" s="43" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D170" s="44" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E170" s="45" t="s">
         <v>14</v>
@@ -8076,7 +8082,7 @@
         <v>14</v>
       </c>
       <c r="G170" s="46" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="H170" s="47" t="s">
         <v>14</v>
@@ -8084,22 +8090,22 @@
     </row>
     <row r="171" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="35" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B171" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C171" s="37" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D171" s="38" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E171" s="39" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F171" s="39" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="G171" s="40" t="s">
         <v>14</v>
@@ -8110,22 +8116,22 @@
     </row>
     <row r="172" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="10" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B172" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C172" s="12" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D172" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E172" s="14" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="F172" s="14" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="G172" s="15" t="s">
         <v>14</v>
@@ -8136,22 +8142,22 @@
     </row>
     <row r="173" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="29" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B173" s="30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C173" s="31" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D173" s="32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E173" s="33" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F173" s="33" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="G173" s="34" t="s">
         <v>14</v>
@@ -8162,22 +8168,22 @@
     </row>
     <row r="174" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="29" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B174" s="30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C174" s="31" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D174" s="32" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E174" s="33" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="F174" s="33" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="G174" s="34" t="s">
         <v>14</v>
@@ -8188,22 +8194,22 @@
     </row>
     <row r="175" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="29" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B175" s="30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C175" s="31" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D175" s="32" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E175" s="33" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F175" s="33" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="G175" s="34" t="s">
         <v>14</v>
@@ -8214,22 +8220,22 @@
     </row>
     <row r="176" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="35" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B176" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C176" s="37" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D176" s="38" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E176" s="39" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F176" s="39" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="G176" s="40" t="s">
         <v>14</v>
@@ -8240,16 +8246,16 @@
     </row>
     <row r="177" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B177" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D177" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E177" s="8" t="s">
         <v>14</v>
@@ -8266,22 +8272,22 @@
     </row>
     <row r="178" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="35" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B178" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C178" s="37" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D178" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E178" s="39" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="F178" s="39" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="G178" s="40" t="s">
         <v>14</v>
@@ -8292,22 +8298,22 @@
     </row>
     <row r="179" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="10" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B179" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C179" s="12" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D179" s="13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E179" s="14" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="F179" s="14" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="G179" s="15" t="s">
         <v>14</v>
@@ -8318,22 +8324,22 @@
     </row>
     <row r="180" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="35" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B180" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C180" s="37" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D180" s="38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E180" s="39" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F180" s="39" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="G180" s="40" t="s">
         <v>14</v>
@@ -8344,16 +8350,16 @@
     </row>
     <row r="181" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="10" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B181" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C181" s="12" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D181" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E181" s="14" t="s">
         <v>14</v>
@@ -8370,22 +8376,22 @@
     </row>
     <row r="182" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="35" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B182" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C182" s="37" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D182" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E182" s="39" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="F182" s="39" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="G182" s="40" t="s">
         <v>14</v>
@@ -8396,16 +8402,16 @@
     </row>
     <row r="183" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="10" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B183" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C183" s="12" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D183" s="13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E183" s="14" t="s">
         <v>14</v>
@@ -8422,22 +8428,22 @@
     </row>
     <row r="184" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="16" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B184" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C184" s="18" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D184" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E184" s="20" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="F184" s="20" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="G184" s="21" t="s">
         <v>14</v>
@@ -8474,7 +8480,7 @@
     </row>
     <row r="186" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -8492,7 +8498,7 @@
         <v>11</v>
       </c>
       <c r="C187" s="43" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D187" s="44" t="s">
         <v>14</v>
@@ -8504,24 +8510,24 @@
         <v>14</v>
       </c>
       <c r="G187" s="46" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H187" s="41" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="188" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B188" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C188" s="12" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D188" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E188" s="14" t="s">
         <v>14</v>
@@ -8533,33 +8539,33 @@
         <v>14</v>
       </c>
       <c r="H188" s="41" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="189" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B189" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C189" s="12" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D189" s="13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E189" s="14" t="s">
+        <v>560</v>
+      </c>
+      <c r="F189" s="14" t="s">
+        <v>561</v>
+      </c>
+      <c r="G189" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H189" s="41" t="s">
         <v>558</v>
-      </c>
-      <c r="F189" s="14" t="s">
-        <v>559</v>
-      </c>
-      <c r="G189" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="H189" s="41" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="190" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8567,91 +8573,91 @@
         <v>10</v>
       </c>
       <c r="B190" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C190" s="37" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D190" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E190" s="39" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="F190" s="39" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="G190" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H190" s="41" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="191" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="35" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B191" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C191" s="37" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D191" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E191" s="39" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="F191" s="39" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="G191" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H191" s="41" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="192" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="35" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B192" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C192" s="37" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D192" s="38" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E192" s="39" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="F192" s="39" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="G192" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H192" s="41" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="193" ht="100" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B193" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C193" s="12" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D193" s="13" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E193" s="14" t="s">
         <v>14</v>
@@ -8663,18 +8669,18 @@
         <v>14</v>
       </c>
       <c r="H193" s="41" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="194" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B194" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D194" s="7" t="s">
         <v>14</v>
@@ -8689,21 +8695,21 @@
         <v>14</v>
       </c>
       <c r="H194" s="41" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="195" ht="82" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="23" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B195" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C195" s="25" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D195" s="26" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E195" s="27" t="s">
         <v>14</v>
@@ -8715,47 +8721,47 @@
         <v>14</v>
       </c>
       <c r="H195" s="41" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="196" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="23" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B196" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C196" s="25" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D196" s="26" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E196" s="27" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="F196" s="27" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="G196" s="28" t="s">
         <v>14</v>
       </c>
       <c r="H196" s="41" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="197" ht="82" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="10" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B197" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C197" s="12" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D197" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E197" s="14" t="s">
         <v>14</v>
@@ -8772,22 +8778,22 @@
     </row>
     <row r="198" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="35" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B198" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C198" s="37" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="D198" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E198" s="39" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="F198" s="39" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G198" s="40" t="s">
         <v>14</v>
@@ -8798,22 +8804,22 @@
     </row>
     <row r="199" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="35" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B199" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C199" s="37" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D199" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E199" s="39" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="F199" s="39" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="G199" s="40" t="s">
         <v>14</v>
@@ -8824,22 +8830,22 @@
     </row>
     <row r="200" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="23" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B200" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C200" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="D200" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C200" s="25" t="s">
-        <v>592</v>
-      </c>
-      <c r="D200" s="26" t="s">
-        <v>27</v>
-      </c>
       <c r="E200" s="27" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="F200" s="27" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="G200" s="28" t="s">
         <v>14</v>
@@ -8850,22 +8856,22 @@
     </row>
     <row r="201" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="29" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B201" s="30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C201" s="31" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D201" s="32" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E201" s="33" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="F201" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="G201" s="34" t="s">
         <v>14</v>
@@ -8876,22 +8882,22 @@
     </row>
     <row r="202" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="35" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B202" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C202" s="37" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="D202" s="38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E202" s="39" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="F202" s="39" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="G202" s="40" t="s">
         <v>14</v>
@@ -8902,16 +8908,16 @@
     </row>
     <row r="203" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="10" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B203" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C203" s="12" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D203" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E203" s="14" t="s">
         <v>14</v>
@@ -8928,16 +8934,16 @@
     </row>
     <row r="204" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B204" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D204" s="7" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E204" s="8" t="s">
         <v>14</v>
@@ -8954,16 +8960,16 @@
     </row>
     <row r="205" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="10" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B205" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C205" s="12" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D205" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E205" s="14" t="s">
         <v>14</v>
@@ -8980,22 +8986,22 @@
     </row>
     <row r="206" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="23" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B206" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C206" s="25" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D206" s="26" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E206" s="27" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="F206" s="27" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="G206" s="28" t="s">
         <v>14</v>
@@ -9006,16 +9012,16 @@
     </row>
     <row r="207" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="10" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B207" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C207" s="12" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D207" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E207" s="14" t="s">
         <v>14</v>
@@ -9032,22 +9038,22 @@
     </row>
     <row r="208" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="16" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B208" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C208" s="18" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D208" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E208" s="20" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="F208" s="20" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="G208" s="21" t="s">
         <v>14</v>
@@ -9084,7 +9090,7 @@
     </row>
     <row r="210" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
@@ -9096,16 +9102,16 @@
     </row>
     <row r="211" ht="262" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="42" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B211" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C211" s="43" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D211" s="44" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E211" s="45" t="s">
         <v>14</v>
@@ -9114,7 +9120,7 @@
         <v>14</v>
       </c>
       <c r="G211" s="46" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="H211" s="47" t="s">
         <v>14</v>
@@ -9122,22 +9128,22 @@
     </row>
     <row r="212" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="35" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B212" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C212" s="37" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="D212" s="38" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E212" s="39" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F212" s="39" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="G212" s="40" t="s">
         <v>14</v>
@@ -9148,22 +9154,22 @@
     </row>
     <row r="213" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="35" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B213" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C213" s="37" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D213" s="38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E213" s="39" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="F213" s="39" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="G213" s="40" t="s">
         <v>14</v>
@@ -9174,22 +9180,22 @@
     </row>
     <row r="214" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="35" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B214" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C214" s="37" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D214" s="38" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E214" s="39" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="F214" s="39" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="G214" s="40" t="s">
         <v>14</v>
@@ -9200,22 +9206,22 @@
     </row>
     <row r="215" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="35" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B215" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C215" s="37" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D215" s="38" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E215" s="39" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="F215" s="39" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="G215" s="40" t="s">
         <v>14</v>
@@ -9226,22 +9232,22 @@
     </row>
     <row r="216" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="29" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B216" s="30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C216" s="31" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D216" s="32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E216" s="33" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="F216" s="33" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="G216" s="34" t="s">
         <v>14</v>
@@ -9252,16 +9258,16 @@
     </row>
     <row r="217" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B217" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="D217" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E217" s="8" t="s">
         <v>14</v>
@@ -9278,16 +9284,16 @@
     </row>
     <row r="218" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="10" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B218" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C218" s="12" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D218" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E218" s="14" t="s">
         <v>14</v>
@@ -9304,16 +9310,16 @@
     </row>
     <row r="219" ht="208" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="42" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B219" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C219" s="43" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D219" s="44" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E219" s="45" t="s">
         <v>14</v>
@@ -9322,7 +9328,7 @@
         <v>14</v>
       </c>
       <c r="G219" s="46" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="H219" s="47" t="s">
         <v>14</v>
@@ -9330,16 +9336,16 @@
     </row>
     <row r="220" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="10" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B220" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C220" s="12" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D220" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E220" s="14" t="s">
         <v>14</v>
@@ -9351,99 +9357,99 @@
         <v>14</v>
       </c>
       <c r="H220" s="41" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="221" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="23" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B221" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C221" s="25" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D221" s="26" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E221" s="27" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="F221" s="27" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="G221" s="28" t="s">
         <v>14</v>
       </c>
       <c r="H221" s="41" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="222" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="10" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B222" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C222" s="12" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="D222" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E222" s="14" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="F222" s="14" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="G222" s="15" t="s">
         <v>14</v>
       </c>
       <c r="H222" s="41" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="223" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="35" t="s">
+        <v>654</v>
+      </c>
+      <c r="B223" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="C223" s="37" t="s">
+        <v>655</v>
+      </c>
+      <c r="D223" s="38" t="s">
+        <v>258</v>
+      </c>
+      <c r="E223" s="39" t="s">
+        <v>651</v>
+      </c>
+      <c r="F223" s="39" t="s">
         <v>652</v>
       </c>
-      <c r="B223" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="C223" s="37" t="s">
-        <v>653</v>
-      </c>
-      <c r="D223" s="38" t="s">
-        <v>254</v>
-      </c>
-      <c r="E223" s="39" t="s">
-        <v>649</v>
-      </c>
-      <c r="F223" s="39" t="s">
-        <v>650</v>
-      </c>
       <c r="G223" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H223" s="41" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="224" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="10" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B224" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C224" s="12" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="D224" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E224" s="14" t="s">
         <v>14</v>
@@ -9455,33 +9461,33 @@
         <v>14</v>
       </c>
       <c r="H224" s="41" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="225" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="16" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B225" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C225" s="18" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="D225" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E225" s="20" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="F225" s="20" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="G225" s="21" t="s">
         <v>14</v>
       </c>
       <c r="H225" s="41" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="226" ht="8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9512,7 +9518,7 @@
     </row>
     <row r="227" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
@@ -9524,13 +9530,13 @@
     </row>
     <row r="228" ht="370" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="48" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B228" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C228" s="49" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="D228" s="50" t="s">
         <v>14</v>
@@ -9542,7 +9548,7 @@
         <v>14</v>
       </c>
       <c r="G228" s="52" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="H228" s="53" t="s">
         <v>14</v>
@@ -9550,22 +9556,22 @@
     </row>
     <row r="229" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="54" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B229" s="55" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C229" s="56" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="D229" s="57" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E229" s="58" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="F229" s="58" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="G229" s="59" t="s">
         <v>14</v>
@@ -9576,16 +9582,16 @@
     </row>
     <row r="230" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B230" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D230" s="7" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="E230" s="8" t="s">
         <v>14</v>
@@ -9602,22 +9608,22 @@
     </row>
     <row r="231" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="54" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B231" s="55" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C231" s="56" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D231" s="57" t="s">
         <v>13</v>
       </c>
       <c r="E231" s="58" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="F231" s="58" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="G231" s="59" t="s">
         <v>14</v>
@@ -9628,13 +9634,13 @@
     </row>
     <row r="232" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B232" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="D232" s="7" t="s">
         <v>14</v>
@@ -9654,16 +9660,16 @@
     </row>
     <row r="233" ht="154" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="42" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B233" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C233" s="43" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="D233" s="44" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E233" s="45" t="s">
         <v>14</v>
@@ -9672,7 +9678,7 @@
         <v>14</v>
       </c>
       <c r="G233" s="46" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="H233" s="47" t="s">
         <v>14</v>
@@ -9680,25 +9686,25 @@
     </row>
     <row r="234" ht="154" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" s="42" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B234" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C234" s="43" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D234" s="44" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E234" s="45" t="s">
+        <v>684</v>
+      </c>
+      <c r="F234" s="45" t="s">
+        <v>685</v>
+      </c>
+      <c r="G234" s="46" t="s">
         <v>682</v>
-      </c>
-      <c r="F234" s="45" t="s">
-        <v>683</v>
-      </c>
-      <c r="G234" s="46" t="s">
-        <v>680</v>
       </c>
       <c r="H234" s="47" t="s">
         <v>14</v>
@@ -9706,16 +9712,16 @@
     </row>
     <row r="235" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="10" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B235" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C235" s="12" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="D235" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E235" s="14" t="s">
         <v>14</v>
@@ -9732,22 +9738,22 @@
     </row>
     <row r="236" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="35" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B236" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C236" s="37" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D236" s="38" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E236" s="39" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="F236" s="39" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="G236" s="40" t="s">
         <v>14</v>
@@ -9758,22 +9764,22 @@
     </row>
     <row r="237" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" s="16" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B237" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C237" s="18" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="D237" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E237" s="20" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="F237" s="20" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="G237" s="21" t="s">
         <v>14</v>
@@ -9810,7 +9816,7 @@
     </row>
     <row r="239" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
@@ -9822,13 +9828,13 @@
     </row>
     <row r="240" ht="514" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" s="48" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B240" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C240" s="49" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D240" s="50" t="s">
         <v>14</v>
@@ -9840,7 +9846,7 @@
         <v>14</v>
       </c>
       <c r="G240" s="52" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="H240" s="53" t="s">
         <v>14</v>
@@ -9848,16 +9854,16 @@
     </row>
     <row r="241" ht="100" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" s="54" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B241" s="55" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C241" s="56" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="D241" s="57" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="E241" s="58" t="s">
         <v>14</v>
@@ -9874,13 +9880,13 @@
     </row>
     <row r="242" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B242" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="D242" s="7" t="s">
         <v>14</v>
@@ -9900,16 +9906,16 @@
     </row>
     <row r="243" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" s="35" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B243" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C243" s="37" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D243" s="38" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E243" s="39" t="s">
         <v>14</v>
@@ -9926,22 +9932,22 @@
     </row>
     <row r="244" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" s="16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B244" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C244" s="18" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="D244" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E244" s="20" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="F244" s="20" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="G244" s="21" t="s">
         <v>14</v>
@@ -9978,7 +9984,7 @@
     </row>
     <row r="246" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
@@ -9990,13 +9996,13 @@
     </row>
     <row r="247" ht="442" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="48" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B247" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C247" s="49" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D247" s="50" t="s">
         <v>13</v>
@@ -10008,7 +10014,7 @@
         <v>14</v>
       </c>
       <c r="G247" s="52" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="H247" s="53" t="s">
         <v>14</v>
@@ -10016,22 +10022,22 @@
     </row>
     <row r="248" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" s="35" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B248" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C248" s="37" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="D248" s="38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E248" s="39" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="F248" s="39" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G248" s="40" t="s">
         <v>14</v>
@@ -10042,22 +10048,22 @@
     </row>
     <row r="249" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" s="23" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B249" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C249" s="25" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D249" s="26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E249" s="27" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="F249" s="27" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="G249" s="28" t="s">
         <v>14</v>
@@ -10068,16 +10074,16 @@
     </row>
     <row r="250" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B250" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C250" s="12" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D250" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E250" s="14" t="s">
         <v>14</v>
@@ -10094,22 +10100,22 @@
     </row>
     <row r="251" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" s="23" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B251" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C251" s="25" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="D251" s="26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E251" s="27" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F251" s="27" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G251" s="28" t="s">
         <v>14</v>
@@ -10123,19 +10129,19 @@
         <v>10</v>
       </c>
       <c r="B252" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C252" s="25" t="s">
+        <v>716</v>
+      </c>
+      <c r="D252" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C252" s="25" t="s">
-        <v>714</v>
-      </c>
-      <c r="D252" s="26" t="s">
-        <v>27</v>
-      </c>
       <c r="E252" s="27" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="F252" s="27" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="G252" s="28" t="s">
         <v>14</v>
@@ -10146,22 +10152,22 @@
     </row>
     <row r="253" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" s="23" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B253" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C253" s="25" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="D253" s="26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E253" s="27" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="F253" s="27" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="G253" s="28" t="s">
         <v>14</v>
@@ -10172,22 +10178,22 @@
     </row>
     <row r="254" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" s="10" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B254" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C254" s="12" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="D254" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E254" s="14" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="F254" s="14" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G254" s="15" t="s">
         <v>14</v>
@@ -10198,22 +10204,22 @@
     </row>
     <row r="255" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" s="35" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B255" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C255" s="37" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="D255" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E255" s="39" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="F255" s="39" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="G255" s="40" t="s">
         <v>14</v>
@@ -10224,22 +10230,22 @@
     </row>
     <row r="256" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" s="23" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B256" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C256" s="25" t="s">
+        <v>729</v>
+      </c>
+      <c r="D256" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C256" s="25" t="s">
-        <v>727</v>
-      </c>
-      <c r="D256" s="26" t="s">
-        <v>27</v>
-      </c>
       <c r="E256" s="27" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="F256" s="27" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="G256" s="28" t="s">
         <v>14</v>
@@ -10250,22 +10256,22 @@
     </row>
     <row r="257" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" s="35" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B257" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C257" s="37" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="D257" s="38" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E257" s="39" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="F257" s="39" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G257" s="40" t="s">
         <v>14</v>
@@ -10276,22 +10282,22 @@
     </row>
     <row r="258" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B258" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C258" s="25" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="D258" s="26" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E258" s="27" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="F258" s="27" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="G258" s="28" t="s">
         <v>14</v>
@@ -10302,22 +10308,22 @@
     </row>
     <row r="259" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B259" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C259" s="6" t="s">
+        <v>737</v>
+      </c>
+      <c r="D259" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E259" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="F259" s="8" t="s">
         <v>735</v>
-      </c>
-      <c r="D259" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E259" s="8" t="s">
-        <v>732</v>
-      </c>
-      <c r="F259" s="8" t="s">
-        <v>733</v>
       </c>
       <c r="G259" s="9" t="s">
         <v>14</v>
@@ -10328,16 +10334,16 @@
     </row>
     <row r="260" ht="82" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" s="29" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B260" s="30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C260" s="31" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="D260" s="32" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="E260" s="33" t="s">
         <v>14</v>
@@ -10354,16 +10360,16 @@
     </row>
     <row r="261" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" s="10" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B261" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C261" s="12" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="D261" s="13" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E261" s="14" t="s">
         <v>14</v>
@@ -10380,22 +10386,22 @@
     </row>
     <row r="262" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" s="16" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B262" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C262" s="18" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="D262" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E262" s="20" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="F262" s="20" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="G262" s="21" t="s">
         <v>14</v>
@@ -10432,7 +10438,7 @@
     </row>
     <row r="264" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
@@ -10444,16 +10450,16 @@
     </row>
     <row r="265" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" s="10" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B265" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C265" s="12" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="D265" s="13" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E265" s="14" t="s">
         <v>14</v>
@@ -10470,22 +10476,22 @@
     </row>
     <row r="266" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B266" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C266" s="12" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="D266" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E266" s="14" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="F266" s="14" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="G266" s="15" t="s">
         <v>14</v>
@@ -10496,25 +10502,25 @@
     </row>
     <row r="267" ht="316" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" s="42" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B267" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C267" s="43" t="s">
+        <v>752</v>
+      </c>
+      <c r="D267" s="44" t="s">
+        <v>753</v>
+      </c>
+      <c r="E267" s="45" t="s">
         <v>750</v>
       </c>
-      <c r="D267" s="44" t="s">
+      <c r="F267" s="45" t="s">
         <v>751</v>
       </c>
-      <c r="E267" s="45" t="s">
-        <v>748</v>
-      </c>
-      <c r="F267" s="45" t="s">
-        <v>749</v>
-      </c>
       <c r="G267" s="46" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="H267" s="47" t="s">
         <v>14</v>
@@ -10522,16 +10528,16 @@
     </row>
     <row r="268" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" s="10" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B268" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C268" s="12" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="D268" s="13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E268" s="14" t="s">
         <v>14</v>
@@ -10548,22 +10554,22 @@
     </row>
     <row r="269" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" s="16" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B269" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C269" s="18" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="D269" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E269" s="20" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="F269" s="20" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="G269" s="21" t="s">
         <v>14</v>
@@ -10600,7 +10606,7 @@
     </row>
     <row r="271" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" s="3" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B271" s="3"/>
       <c r="C271" s="3"/>
@@ -10612,22 +10618,22 @@
     </row>
     <row r="272" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" s="10" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B272" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C272" s="12" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="D272" s="13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E272" s="14" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="F272" s="14" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="G272" s="15" t="s">
         <v>14</v>
@@ -10638,25 +10644,25 @@
     </row>
     <row r="273" ht="82" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" s="42" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B273" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C273" s="43" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="D273" s="44" t="s">
+        <v>753</v>
+      </c>
+      <c r="E273" s="45" t="s">
+        <v>750</v>
+      </c>
+      <c r="F273" s="45" t="s">
         <v>751</v>
       </c>
-      <c r="E273" s="45" t="s">
-        <v>748</v>
-      </c>
-      <c r="F273" s="45" t="s">
-        <v>749</v>
-      </c>
       <c r="G273" s="46" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="H273" s="47" t="s">
         <v>14</v>
@@ -10664,16 +10670,16 @@
     </row>
     <row r="274" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" s="10" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B274" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C274" s="12" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="D274" s="13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E274" s="14" t="s">
         <v>14</v>
@@ -10690,22 +10696,22 @@
     </row>
     <row r="275" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" s="16" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B275" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C275" s="18" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D275" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E275" s="20" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="F275" s="20" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="G275" s="21" t="s">
         <v>14</v>
@@ -10742,7 +10748,7 @@
     </row>
     <row r="277" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" s="3" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B277" s="3"/>
       <c r="C277" s="3"/>
@@ -10754,16 +10760,16 @@
     </row>
     <row r="278" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B278" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C278" s="12" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="D278" s="13" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E278" s="14" t="s">
         <v>14</v>
@@ -10780,42 +10786,42 @@
     </row>
     <row r="279" ht="730" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" s="48" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B279" s="30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C279" s="49" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="D279" s="50" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E279" s="51" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="F279" s="51" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="G279" s="52" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="H279" s="41" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
     </row>
     <row r="280" ht="82" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" s="10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B280" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C280" s="12" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="D280" s="13" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E280" s="14" t="s">
         <v>14</v>
@@ -10827,47 +10833,47 @@
         <v>14</v>
       </c>
       <c r="H280" s="41" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
     </row>
     <row r="281" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" s="23" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B281" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C281" s="25" t="s">
+        <v>777</v>
+      </c>
+      <c r="D281" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C281" s="25" t="s">
-        <v>775</v>
-      </c>
-      <c r="D281" s="26" t="s">
-        <v>27</v>
-      </c>
       <c r="E281" s="27" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="F281" s="27" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="G281" s="28" t="s">
         <v>14</v>
       </c>
       <c r="H281" s="41" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
     </row>
     <row r="282" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" s="10" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B282" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C282" s="12" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="D282" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E282" s="14" t="s">
         <v>14</v>
@@ -10884,16 +10890,16 @@
     </row>
     <row r="283" ht="82" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" s="35" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B283" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C283" s="37" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="D283" s="38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E283" s="39" t="s">
         <v>14</v>
@@ -10905,27 +10911,27 @@
         <v>14</v>
       </c>
       <c r="H283" s="41" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
     </row>
     <row r="284" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" s="10" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B284" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C284" s="12" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D284" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E284" s="14" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="F284" s="14" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="G284" s="15" t="s">
         <v>14</v>
@@ -10936,48 +10942,48 @@
     </row>
     <row r="285" ht="136" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" s="35" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B285" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C285" s="37" t="s">
+        <v>789</v>
+      </c>
+      <c r="D285" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="E285" s="39" t="s">
         <v>787</v>
       </c>
-      <c r="D285" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="E285" s="39" t="s">
-        <v>785</v>
-      </c>
       <c r="F285" s="39" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="G285" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H285" s="41" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
     </row>
     <row r="286" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" s="10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B286" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C286" s="12" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="D286" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E286" s="14" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="F286" s="14" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="G286" s="15" t="s">
         <v>14</v>
@@ -10988,48 +10994,48 @@
     </row>
     <row r="287" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" s="35" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B287" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C287" s="37" t="s">
+        <v>794</v>
+      </c>
+      <c r="D287" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="E287" s="39" t="s">
         <v>792</v>
       </c>
-      <c r="D287" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="E287" s="39" t="s">
-        <v>790</v>
-      </c>
       <c r="F287" s="39" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="G287" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H287" s="41" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
     </row>
     <row r="288" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" s="10" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B288" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C288" s="12" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="D288" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E288" s="14" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F288" s="14" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="G288" s="15" t="s">
         <v>14</v>
@@ -11040,42 +11046,42 @@
     </row>
     <row r="289" ht="100" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" s="35" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B289" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C289" s="37" t="s">
+        <v>799</v>
+      </c>
+      <c r="D289" s="38" t="s">
+        <v>800</v>
+      </c>
+      <c r="E289" s="39" t="s">
         <v>797</v>
       </c>
-      <c r="D289" s="38" t="s">
+      <c r="F289" s="39" t="s">
         <v>798</v>
       </c>
-      <c r="E289" s="39" t="s">
-        <v>795</v>
-      </c>
-      <c r="F289" s="39" t="s">
-        <v>796</v>
-      </c>
       <c r="G289" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H289" s="41" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
     </row>
     <row r="290" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B290" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C290" s="12" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="D290" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E290" s="14" t="s">
         <v>14</v>
@@ -11092,42 +11098,42 @@
     </row>
     <row r="291" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" s="35" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B291" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C291" s="37" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="D291" s="38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E291" s="39" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="F291" s="39" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="G291" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H291" s="41" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
     </row>
     <row r="292" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" s="10" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B292" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C292" s="12" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="D292" s="13" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E292" s="14" t="s">
         <v>14</v>
@@ -11144,28 +11150,28 @@
     </row>
     <row r="293" ht="100" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" s="16" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B293" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C293" s="18" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="D293" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E293" s="20" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="F293" s="20" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="G293" s="21" t="s">
         <v>14</v>
       </c>
       <c r="H293" s="41" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
     </row>
     <row r="294" ht="8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11196,7 +11202,7 @@
     </row>
     <row r="295" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" s="3" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="B295" s="3"/>
       <c r="C295" s="3"/>
@@ -11214,10 +11220,10 @@
         <v>11</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="D296" s="7" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="E296" s="8" t="s">
         <v>14</v>
@@ -11237,19 +11243,19 @@
         <v>14</v>
       </c>
       <c r="B297" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C297" s="18" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="D297" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E297" s="20" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="F297" s="20" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="G297" s="21" t="s">
         <v>14</v>
@@ -11286,7 +11292,7 @@
     </row>
     <row r="299" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" s="3" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B299" s="3"/>
       <c r="C299" s="3"/>
@@ -11298,16 +11304,16 @@
     </row>
     <row r="300" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" s="10" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B300" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C300" s="12" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="D300" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E300" s="14" t="s">
         <v>14</v>
@@ -11324,22 +11330,22 @@
     </row>
     <row r="301" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" s="23" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B301" s="24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C301" s="25" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="D301" s="26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E301" s="27" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="F301" s="27" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="G301" s="28" t="s">
         <v>14</v>
@@ -11350,22 +11356,22 @@
     </row>
     <row r="302" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" s="35" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B302" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C302" s="37" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="D302" s="38" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E302" s="39" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F302" s="39" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G302" s="40" t="s">
         <v>14</v>
@@ -11376,22 +11382,22 @@
     </row>
     <row r="303" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" s="35" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B303" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C303" s="37" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="D303" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E303" s="39" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="F303" s="39" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="G303" s="40" t="s">
         <v>14</v>
@@ -11402,22 +11408,22 @@
     </row>
     <row r="304" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" s="29" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B304" s="30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C304" s="31" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="D304" s="32" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="E304" s="33" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="F304" s="33" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="G304" s="34" t="s">
         <v>14</v>
@@ -11428,22 +11434,22 @@
     </row>
     <row r="305" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" s="23" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B305" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C305" s="25" t="s">
+        <v>835</v>
+      </c>
+      <c r="D305" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C305" s="25" t="s">
-        <v>833</v>
-      </c>
-      <c r="D305" s="26" t="s">
-        <v>27</v>
-      </c>
       <c r="E305" s="27" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="F305" s="27" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="G305" s="28" t="s">
         <v>14</v>
@@ -11454,16 +11460,16 @@
     </row>
     <row r="306" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" s="10" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B306" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C306" s="12" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="D306" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E306" s="14" t="s">
         <v>14</v>
@@ -11480,13 +11486,13 @@
     </row>
     <row r="307" ht="46" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" s="4" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B307" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C307" s="6" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="D307" s="7" t="s">
         <v>14</v>
@@ -11501,27 +11507,27 @@
         <v>14</v>
       </c>
       <c r="H307" s="41" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
     </row>
     <row r="308" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" s="16" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B308" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C308" s="18" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="D308" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E308" s="20" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="F308" s="20" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="G308" s="21" t="s">
         <v>14</v>
@@ -11558,7 +11564,7 @@
     </row>
     <row r="310" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" s="3" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B310" s="3"/>
       <c r="C310" s="3"/>
@@ -11570,16 +11576,16 @@
     </row>
     <row r="311" ht="82" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" s="10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B311" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C311" s="12" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="D311" s="13" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="E311" s="14" t="s">
         <v>14</v>
@@ -11591,7 +11597,7 @@
         <v>14</v>
       </c>
       <c r="H311" s="41" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="312" ht="8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11671,7 +11677,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11683,22 +11689,22 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>5</v>
@@ -11709,7 +11715,7 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="60" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B3" s="60"/>
       <c r="C3" s="60"/>
@@ -11721,22 +11727,22 @@
     </row>
     <row r="4" ht="55" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="61" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B4" s="62" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C4" s="63" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="D4" s="64" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="E4" s="62" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="F4" s="62" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="G4" s="65">
         <v>38.298</v>
@@ -11747,22 +11753,22 @@
     </row>
     <row r="5" ht="55" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="61" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B5" s="62" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C5" s="63" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="D5" s="64" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="E5" s="62" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="F5" s="62" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="G5" s="65">
         <v>38.297</v>
@@ -11773,22 +11779,22 @@
     </row>
     <row r="6" ht="55" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="61" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B6" s="62" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C6" s="63" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="D6" s="64" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="E6" s="62" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="F6" s="62" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="G6" s="65">
         <v>38.305</v>
@@ -11799,7 +11805,7 @@
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="60" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B7" s="60"/>
       <c r="C7" s="60"/>
@@ -11811,22 +11817,22 @@
     </row>
     <row r="8" ht="55" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="61" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B8" s="62" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="D8" s="64" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="E8" s="62" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="F8" s="62" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="G8" s="65">
         <v>37.269</v>
@@ -11837,22 +11843,22 @@
     </row>
     <row r="9" ht="55" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="61" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B9" s="62" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C9" s="63" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="D9" s="64" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E9" s="62" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="F9" s="62" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="G9" s="65">
         <v>37.298</v>
@@ -11863,22 +11869,22 @@
     </row>
     <row r="10" ht="55" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="61" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B10" s="62" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C10" s="63" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="D10" s="64" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="E10" s="62" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="F10" s="62" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="G10" s="65">
         <v>37.255</v>
@@ -11889,22 +11895,22 @@
     </row>
     <row r="11" ht="55" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="66" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="B11" s="67" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C11" s="68" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="D11" s="69" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="E11" s="67" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="F11" s="67" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="G11" s="70">
         <v>37.22</v>
@@ -11915,7 +11921,7 @@
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="60" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B12" s="60"/>
       <c r="C12" s="60"/>
@@ -11927,22 +11933,22 @@
     </row>
     <row r="13" ht="55" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="61" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B13" s="62" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C13" s="63" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="D13" s="64" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="E13" s="62" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="F13" s="62" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="G13" s="65">
         <v>37.199</v>
@@ -11953,22 +11959,22 @@
     </row>
     <row r="14" ht="55" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="66" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="B14" s="67" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C14" s="68" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="D14" s="69" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="E14" s="67" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="F14" s="67" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="G14" s="70">
         <v>36.999</v>
@@ -11979,7 +11985,7 @@
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="60" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B15" s="60"/>
       <c r="C15" s="60"/>
@@ -11991,22 +11997,22 @@
     </row>
     <row r="16" ht="55" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="71" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B16" s="72" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="C16" s="73" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="D16" s="74" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="E16" s="72" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="F16" s="72" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="G16" s="75" t="s">
         <v>14</v>
@@ -12017,22 +12023,22 @@
     </row>
     <row r="17" ht="55" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="71" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B17" s="72" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="C17" s="73" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="D17" s="74" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="E17" s="72" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="F17" s="72" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="G17" s="75" t="s">
         <v>14</v>
@@ -12043,22 +12049,22 @@
     </row>
     <row r="18" ht="55" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="71" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B18" s="72" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="C18" s="73" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="D18" s="74" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="E18" s="72" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="F18" s="72" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="G18" s="75">
         <v>38.57</v>
@@ -12069,22 +12075,22 @@
     </row>
     <row r="19" ht="55" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="71" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B19" s="72" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C19" s="73" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="D19" s="74" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="E19" s="72" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="F19" s="72" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="G19" s="75" t="s">
         <v>14</v>
@@ -12095,22 +12101,22 @@
     </row>
     <row r="20" ht="55" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="71" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B20" s="72" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C20" s="73" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="D20" s="74" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="E20" s="72" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="F20" s="72" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="G20" s="75" t="s">
         <v>14</v>
@@ -12121,22 +12127,22 @@
     </row>
     <row r="21" ht="55" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="71" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B21" s="72" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="C21" s="73" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="D21" s="74" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="E21" s="72" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="F21" s="72" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="G21" s="75">
         <v>36.43</v>
@@ -12147,22 +12153,22 @@
     </row>
     <row r="22" ht="55" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="71" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B22" s="72" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="C22" s="73" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="D22" s="74" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="E22" s="72" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="F22" s="72" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="G22" s="75">
         <v>36.864</v>
@@ -12173,22 +12179,22 @@
     </row>
     <row r="23" ht="55" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="71" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B23" s="72" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="C23" s="73" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="D23" s="74" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="E23" s="72" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="F23" s="72" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="G23" s="75">
         <v>37.787</v>
@@ -12222,7 +12228,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="76" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B1" s="76"/>
     </row>
@@ -12239,47 +12245,47 @@
         <v>16</v>
       </c>
       <c r="B3" s="78" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="79" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="80" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="81" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B5" s="82" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="83" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B6" s="84" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="85" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B7" s="86" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="87" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -12287,23 +12293,23 @@
         <v>11</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="91" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B10" s="92" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="93" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="B11" s="94" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -12316,7 +12322,7 @@
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="76" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="B13" s="76"/>
     </row>
@@ -12330,42 +12336,42 @@
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="95" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B15" s="96" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="95" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="B16" s="96" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="95" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="B17" s="96" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="95" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="B18" s="96" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="95" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="B19" s="96" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
     </row>
   </sheetData>
@@ -12395,7 +12401,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="76" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="B1" s="76"/>
       <c r="C1" s="76"/>
@@ -12404,19 +12410,19 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="97" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="B2" s="97" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="C2" s="97" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="D2" s="97" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="E2" s="97" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
     </row>
   </sheetData>

--- a/mom-trip-days-1-24.xlsx
+++ b/mom-trip-days-1-24.xlsx
@@ -157,10 +157,10 @@
     <t>Courthouse Towers — pull over by the road, look at the huge red rock towers rising from the desert, and take photos.</t>
   </si>
   <si>
-    <t>38.63255</t>
-  </si>
-  <si>
-    <t>-109.60238</t>
+    <t>38.63718</t>
+  </si>
+  <si>
+    <t>-109.60019</t>
   </si>
   <si>
     <t>9:30 AM</t>
